--- a/01.SOMD/02.metadata_structure/02_SOMD_search_eq.xlsx
+++ b/01.SOMD/02.metadata_structure/02_SOMD_search_eq.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/01.SOMD/01.metadata_structure/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cgiar.sharepoint.com/sites/Alliance-AgroecologyKnowledgeHub/Shared Documents/General/Agroecology_Evidence_Hub/01.SOMD/02.metadata_structure/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="525" documentId="8_{3DBE2D00-5402-43EC-822D-A8757C7CA091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E660F0AA-4609-40FC-842F-D55F4958CD07}"/>
+  <xr:revisionPtr revIDLastSave="545" documentId="8_{3DBE2D00-5402-43EC-822D-A8757C7CA091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FE70BB6-8F81-47A0-B43E-F9B4CA8A5225}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3075" yWindow="2835" windowWidth="21600" windowHeight="11175" xr2:uid="{6CF94B49-C55C-417E-8862-D75FC6347405}"/>
+    <workbookView xWindow="28680" yWindow="870" windowWidth="29040" windowHeight="15720" xr2:uid="{6CF94B49-C55C-417E-8862-D75FC6347405}"/>
   </bookViews>
   <sheets>
     <sheet name="03_SOMD_search_eq" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="115">
   <si>
     <t>search_strategy</t>
   </si>
@@ -77,18 +77,6 @@
   </si>
   <si>
     <t>SOMD</t>
-  </si>
-  <si>
-    <t>Evidence library of meta-analytical literature assessing the sustainability of agriculture – a dataset.</t>
-  </si>
-  <si>
-    <t>Schievano, A., Perez-Soba, M., Bosco, S., Montero-Castano, A., Catarino, R., Chen, M., Tamburini, G., Landoni, B., Mantegazza, O., Guerrero, I., Bielza, M., Assouline, M., Koeble, R., Dentener, F., Van der Velde, M., Rega, C., Furlan, A., Paracchini, M. L., Weiss, F., Angileri, V., Terres, J.-M., Makowski, D.</t>
-  </si>
-  <si>
-    <t>Sci. Data</t>
-  </si>
-  <si>
-    <t>10.1038/s41597-024-03682-6</t>
   </si>
   <si>
     <t>Dataset section</t>
@@ -383,9 +371,6 @@
     <t>RTE_WOS_26.04.2026</t>
   </si>
   <si>
-    <t>Schievano et al 2024</t>
-  </si>
-  <si>
     <t>Research Team Evidence (MFL except alliance)</t>
   </si>
   <si>
@@ -402,13 +387,31 @@
   </si>
   <si>
     <t>n_records</t>
+  </si>
+  <si>
+    <t>10.2905/JRC.5E630Q8</t>
+  </si>
+  <si>
+    <t>European Commission, Joint Research Centre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bosco, S., Schievano, Andrea; Murugan Rajasekaran; Bielza, Maria; Chen, Mathilde; Kay, Sonja; Rubeaud, Camille; Kothke, Margret; Catarino, Rui; Tamburini, Giovanni; Mantegazza, Otho; Guerrero, Irene; Perez-Soba, Marta; Montero-Castano, Ana; Landoni, Beatrice; Koeble, Renate; Dentener, Frank; Rega, Carlo; Furlan, Andrea; Paracchini, Maria Luisa; Weiss, Franz; Angileri, Vincenzo; Hagyo, Andrea; Van der Velde, Marijn; Terres, Jean-Michel; Makowski, David (2026):  – Evidence library on the qualitative and quantitative effects of sustainable farming practices on climate, environment, and productivity. </t>
+  </si>
+  <si>
+    <t>JRC Farming Practices dataset (version 2026)</t>
+  </si>
+  <si>
+    <t>Evidence library on the qualitative and quantitative effects of sustainable farming practices on climate, environment, and productivity</t>
+  </si>
+  <si>
+    <t>6742 (26/05/2026)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -498,6 +501,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF26324B"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -593,7 +602,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -619,6 +628,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1300,7 +1310,7 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="K1" t="s">
         <v>9</v>
@@ -1309,65 +1319,65 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" ht="15.75">
       <c r="A2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="E2" s="4">
-        <v>2024</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>16</v>
+        <v>2026</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="G2" s="21" t="s">
+        <v>109</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
       <c r="J2">
-        <v>13935</v>
+        <v>14949</v>
       </c>
       <c r="K2" s="3" t="str">
         <f>_03_SOMD_search_eq[[#This Row],[ss_type]]&amp; "_" &amp; LEFT(_03_SOMD_search_eq[[#This Row],[search_database_authors]],5) &amp; "_" &amp; RIGHT(_03_SOMD_search_eq[[#This Row],[search_database_year]],2) &amp; "_" &amp; LEFT(_03_SOMD_search_eq[[#This Row],[search_database_title]],5) &amp; "_" &amp; LEFT(_03_SOMD_search_eq[[#This Row],[search_database_journal]],2)</f>
-        <v>SOMD_Schie_24_Evide_Sc</v>
-      </c>
-      <c r="L2">
-        <v>13935</v>
+        <v>SOMD_Bosco_26_Evide_Eu</v>
+      </c>
+      <c r="L2" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1">
       <c r="A3" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="I3" s="19">
         <v>46138</v>
@@ -1376,34 +1386,34 @@
         <v>161</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="L3" s="7"/>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I4" s="19">
         <v>46138</v>
@@ -1412,34 +1422,34 @@
         <v>49</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="L4" s="7"/>
     </row>
     <row r="5" spans="1:12" s="12" customFormat="1">
       <c r="A5" s="12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E5" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>102</v>
-      </c>
       <c r="G5" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="I5" s="16">
         <v>46145</v>
@@ -1452,28 +1462,28 @@
     </row>
     <row r="6" spans="1:12" s="12" customFormat="1">
       <c r="A6" s="12" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G6" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" s="15" t="s">
         <v>97</v>
-      </c>
-      <c r="H6" s="15" t="s">
-        <v>101</v>
       </c>
       <c r="I6" s="16">
         <v>46145</v>
@@ -1513,7 +1523,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B1" s="2">
         <v>3</v>
@@ -1521,31 +1531,31 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>11</v>
@@ -1553,42 +1563,42 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
         <v>31</v>
       </c>
-      <c r="B8" t="s">
+      <c r="F8" t="s">
         <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1596,19 +1606,19 @@
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1616,19 +1626,19 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1636,19 +1646,19 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1656,19 +1666,19 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1676,19 +1686,19 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1696,19 +1706,19 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1716,39 +1726,39 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" t="s">
         <v>60</v>
-      </c>
-      <c r="C15" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" t="s">
-        <v>63</v>
-      </c>
-      <c r="F15" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" t="s">
         <v>65</v>
-      </c>
-      <c r="C16" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" t="s">
-        <v>68</v>
-      </c>
-      <c r="F16" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1756,19 +1766,19 @@
         <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -1776,19 +1786,19 @@
         <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F18" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1809,14 +1819,14 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1824,11 +1834,11 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1836,44 +1846,44 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1887,14 +1897,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2099,27 +2107,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4b26243c-b736-4d9c-b036-479be2ad88a1">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="432dd258-9dce-4cb3-b611-c68c0fbce7f3" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2A8A660-9284-4780-8ED0-4709E9BB833A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AEDD599-11B4-46FE-854D-9923ECF7E41C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2144,9 +2145,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AEDD599-11B4-46FE-854D-9923ECF7E41C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2A8A660-9284-4780-8ED0-4709E9BB833A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="432dd258-9dce-4cb3-b611-c68c0fbce7f3"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="4b26243c-b736-4d9c-b036-479be2ad88a1"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>